--- a/099-納品物/020-内部_プログラミング設計/021-クラス図/購入機能/021-クラス図_購入機能_.xlsx
+++ b/099-納品物/020-内部_プログラミング設計/021-クラス図/購入機能/021-クラス図_購入機能_.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\099-納品物\020-内部_プログラミング設計\021-クラス図\購入機能\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\020-内部_プログラミング設計\021-クラス図\購入機能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8EE782-8856-48C1-9834-E516D6D9D5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3167A1C-8C2F-4D2B-A16E-AE691686F896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3852" yWindow="1440" windowWidth="17280" windowHeight="10536" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="10" r:id="rId1"/>
@@ -179,18 +179,9 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>ショッピング機能：商品検索画面（メイン画面）</t>
-    <rPh sb="9" eb="11">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ガメン</t>
+    <t>ショッピング機能：購入機能</t>
+    <rPh sb="9" eb="13">
+      <t>コウニュウキノウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1116,23 +1107,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>99262</xdr:rowOff>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>26474</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66EC9D88-A1E9-4AA0-B4F1-E229940384CE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C0C79B1-3465-4288-8686-E5230754BEA2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1148,15 +1139,15 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="381000" y="1112520"/>
-          <a:ext cx="7772400" cy="6705802"/>
+          <a:off x="342900" y="1114425"/>
+          <a:ext cx="7774305" cy="5646224"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln w="12700">
+        <a:ln w="28575">
           <a:solidFill>
-            <a:schemeClr val="tx1"/>
+            <a:sysClr val="windowText" lastClr="000000"/>
           </a:solidFill>
         </a:ln>
       </xdr:spPr>
